--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -14,8 +14,11 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="02-03" sheetId="7" r:id="rId7"/>
+    <x:sheet name="09-03" sheetId="8" r:id="rId8"/>
   </x:sheets>
-  <x:definedNames/>
+  <x:definedNames>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'09-03'!$A$2:$P$65</x:definedName>
+  </x:definedNames>
   <x:calcPr calcId="191029"/>
   <x:extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -865,6 +868,585 @@
   </x:si>
   <x:si>
     <x:t>CK Đủ 100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lữ Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76 Quang Trung Tăng nhơn phú B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>An Tam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-03-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yến Linh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>183/50 đường số 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-03-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LêNguyễn Hải Đăng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136561</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17 Mai Chí Thọ, P An Khánh, chung cư Newcity toà venice 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136492</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86/22 thống nhất p10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quyen Nguyễn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136621</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Địa chỉ: 220/36/33 Nguyễn Văn khối p9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>việt hoàng - fb Ly Ly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62 đường số 4 cư xá đô thành</x:t>
+  </x:si>
+  <x:si>
+    <x:t>đã ck</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thuy Tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136659</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132 bến vân đồn f6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-03-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>W3227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>375 tân thời hiệp 21, Tổ 3 Kp3 ( nhớ gõ đủ)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hi Ha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136438</x:t>
+  </x:si>
+  <x:si>
+    <x:t>căn hộ florita - tòa A đường c4, phường Tân Hưng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trinh @gpt107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136672</x:t>
+  </x:si>
+  <x:si>
+    <x:t>162A/1 Tiên Quang Diệu, KP., Phường An Phú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ny-069 294154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136604</x:t>
+  </x:si>
+  <x:si>
+    <x:t>301 Phuong Pham Ngu Lao Street, District 1, Ho</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jerry Lai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136264</x:t>
+  </x:si>
+  <x:si>
+    <x:t>341/18 xvnt p24 binh thanh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nhận hộ 15 Nguyễn Hà</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136448</x:t>
+  </x:si>
+  <x:si>
+    <x:t>433/11/2 LÊ ĐỨC THỌ, Phường 17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/03/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Su Su</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26/33 đường số 59-p14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>boramey 015738168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhà xe khải nam 365 hùng vương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabee2530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>275/14b1, Đ. Đặng Nguyên Cẩn, Phường 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>183/50 đường số 28 phường an nhơn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gộp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bảo Trân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136277</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44/1 yên đỗ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Thị Mỹ Quyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136315</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Địa chỉ: 334 tô hiến thành p14 Chung cư kingdom block A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trang Hồ Vĩnh Như</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35 đặng đức thuật, chung cư RIVERPARK PREMIER Block A, p.Tân Phong ( kế bên tiệm bánh tour les jours)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Quỳnh Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>147 đường số An Miên spa an khánh spa an miên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tô Hà Vi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>k04,05 chung cư kingston 223 Đ. Hoàng Văn Thụ, Ward 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mẫn Dương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55 đường 39 kdc Vạn Phúc hiệp bình</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiều fb Alula Phạm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136668</x:t>
+  </x:si>
+  <x:si>
+    <x:t>140B phan văn khoẻ p2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bích Huyền</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD135961</x:t>
+  </x:si>
+  <x:si>
+    <x:t>453/120/49A, Lê Văn Khương, Hiệp Thành</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-03-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nhi Le</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>743/11/10 Hồng Bàng P6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amy VD Tran</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136240</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85/8 Nguyễn Hồng Đào phường 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thơm Thơm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119 nguyễn văn công p. Hạnh thông</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Thị Kim Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K3.37 số 36 đường D15A KDC Hưng Phú P. Phước Long B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phẩm Huỳnh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84 phạm Hồng thái phường bến thành</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tuyết Nguyễn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91/5/17 đường 8 linh trung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Ngọc Phương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50 lê trực phường 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Thị Như Ý</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136498</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48 Cô Bắc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thu Thương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136397</x:t>
+  </x:si>
+  <x:si>
+    <x:t>554/11 p13 cộng hoà</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-03-2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quyên Trần</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136680</x:t>
+  </x:si>
+  <x:si>
+    <x:t>184 trần văn kiều p10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thy Hồng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136295</x:t>
+  </x:si>
+  <x:si>
+    <x:t>361/23/3 phan huy ích p14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@ca200788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136606</x:t>
+  </x:si>
+  <x:si>
+    <x:t>d/c 357/3 Trần Phú Phường 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồng Phương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dc: Empire city - Toà Linden 283 Mai Chí Thọ, Phường Thủ Thiêm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thuy Tien Le</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chung cư Safira Khang điền 454 võ chí công</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinh Phạm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chung Cư Sadora, C - 06.02 C - 06.02, Khu Phố 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>310 phạm văn chiêu, p9, gvap</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giáng Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111 đường số 10 phường 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Lê Bích Ngọc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>324/9/4 Lý Thường Kiệt, F14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loan Nguyễn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136612</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74 Trường Sa, P.17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hiếu Nguyễn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>495/18 tô hiến thành, phường 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136563</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Thị Thanh Hà</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136620</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/7 thanh đa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Trang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132 đường 39 tân quy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BN182 miki</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163 Đường Trương Thị Hoa, phường Tân Thới Hiệp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>parichat jaiduang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central 2 Building (C2), Vinhomes Central Park, 208 Nguyen H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emily</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36/15 yên thế p2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Note : Bống Kẹo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124 đường 24b bình trị đông binh tân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Lan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD136367</x:t>
+  </x:si>
+  <x:si>
+    <x:t>545/16/35A nguyễn xiển, p.long thạnh mỹ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SỈ VIVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>279 Đường 3/2 phường Vườn Lài</x:t>
+  </x:si>
+  <x:si>
+    <x:t>W2459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>375 tân thới hiệp 21, Tổ 3, Kp3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name-May Oo(Isabella) Lavita Charm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58 Đường Số 1, Trường Thọ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jess-9244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>275/14B1 Đặng Nguyễn Cẩn, Phường Phú Lâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ari Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16-18 đường số 5, P. Hạnh Thông: Phòng 001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T7.7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tiền hàng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trừ Ship</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cước xử</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tiền lấy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khách C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giảm tiền</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hàng Boom Trả</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trừ đơn cũ đã ck</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tổng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CN.8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T2.9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T6.6.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T7.8.3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -906,7 +1488,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -936,6 +1518,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC87C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1101,7 +1688,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1184,8 +1771,17 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1292,6 +1888,18 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -4489,4 +5097,3025 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:S65"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.335625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.085625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33.085625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.210625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="93.960625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.960625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.085625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.585625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11.585625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.835625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.460625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9.085625" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.335625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11.210625" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="4.835625" style="0" customWidth="1"/>
+    <x:col min="17" max="19" width="8.460625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2" spans="1:19">
+      <x:c r="A2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="R2" s="1" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="S2" s="1" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:19">
+      <x:c r="B3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F3" s="2">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G3" s="2">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="H3" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I3" s="2">
+        <x:f>G3-H3</x:f>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:19">
+      <x:c r="B4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G4" s="2">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="H4" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I4" s="2">
+        <x:f>G4-H4</x:f>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:19">
+      <x:c r="B5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F5" s="2">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G5" s="2">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="H5" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I5" s="2">
+        <x:f>G5-H5</x:f>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:19">
+      <x:c r="B6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G6" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I6" s="2">
+        <x:f>-H6</x:f>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:19">
+      <x:c r="B7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G7" s="2">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="H7" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I7" s="2">
+        <x:f>G7-H7</x:f>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:19">
+      <x:c r="B8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F8" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I8" s="2">
+        <x:f>-H8</x:f>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:19">
+      <x:c r="B9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F9" s="2">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="2">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="H9" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I9" s="2">
+        <x:f>G9-H9</x:f>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:19">
+      <x:c r="B10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F10" s="2">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I10" s="2">
+        <x:f>-H10</x:f>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:19">
+      <x:c r="B11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F11" s="2">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G11" s="2">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="H11" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I11" s="2">
+        <x:f>G11-H11</x:f>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:19">
+      <x:c r="B12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F12" s="2">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="2">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="H12" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I12" s="2">
+        <x:f>G12-H12</x:f>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:19">
+      <x:c r="B13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G13" s="2">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="H13" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I13" s="2">
+        <x:f>G13-H13</x:f>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:19">
+      <x:c r="B14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F14" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I14" s="2">
+        <x:f>-H14</x:f>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:19">
+      <x:c r="B15" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="2">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H15" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I15" s="2">
+        <x:f>G15-H15</x:f>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:19">
+      <x:c r="B16" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G16" s="2">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="H16" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I16" s="2">
+        <x:f>G16-H16</x:f>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:19">
+      <x:c r="B17" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G17" s="2">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H17" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I17" s="2">
+        <x:f>G17-H17</x:f>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:19">
+      <x:c r="B18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F18" s="2">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G18" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I18" s="2">
+        <x:f>-H18</x:f>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:19">
+      <x:c r="B19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F19" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G19" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I19" s="2">
+        <x:f>-H19</x:f>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:19">
+      <x:c r="B20" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G20" s="2">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="H20" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I20" s="2">
+        <x:f>G20-H20</x:f>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M20" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:19">
+      <x:c r="B21" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G21" s="2">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="H21" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I21" s="2">
+        <x:f>G21-H21</x:f>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:19">
+      <x:c r="B22" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="F22" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G22" s="2">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="H22" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I22" s="2">
+        <x:f>G22-H22</x:f>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L22" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:19">
+      <x:c r="B23" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="F23" s="2">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G23" s="2">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="H23" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I23" s="2">
+        <x:f>G23-H23</x:f>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:19">
+      <x:c r="B24" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="F24" s="2">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="2">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="H24" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I24" s="2">
+        <x:f>G24-H24</x:f>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:19">
+      <x:c r="B25" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G25" s="2">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="H25" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I25" s="2">
+        <x:f>G25-H25</x:f>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:19">
+      <x:c r="B26" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G26" s="2">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="H26" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I26" s="2">
+        <x:f>G26-H26</x:f>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:19">
+      <x:c r="B27" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="F27" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G27" s="2">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="H27" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I27" s="2">
+        <x:f>G27-H27</x:f>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:19">
+      <x:c r="B28" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F28" s="2">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I28" s="2">
+        <x:f>-H28</x:f>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:19">
+      <x:c r="B29" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="F29" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G29" s="2">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="H29" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I29" s="2">
+        <x:f>G29-H29</x:f>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:19">
+      <x:c r="B30" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G30" s="2">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="H30" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I30" s="2">
+        <x:f>G30-H30</x:f>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:19">
+      <x:c r="B31" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G31" s="2">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="H31" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I31" s="2">
+        <x:f>G31-H31</x:f>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:19">
+      <x:c r="B32" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="F32" s="2">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G32" s="2">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="H32" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I32" s="2">
+        <x:f>G32-H32</x:f>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:19">
+      <x:c r="B33" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F33" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I33" s="2">
+        <x:f>-H33</x:f>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:19">
+      <x:c r="B34" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G34" s="2">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="H34" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I34" s="2">
+        <x:f>G34-H34</x:f>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:19">
+      <x:c r="B35" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="F35" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G35" s="2">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="H35" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I35" s="2">
+        <x:f>G35-H35</x:f>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M35" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:19">
+      <x:c r="B36" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G36" s="2">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H36" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I36" s="2">
+        <x:f>G36-H36</x:f>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:19">
+      <x:c r="B37" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="F37" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="2">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="H37" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I37" s="2">
+        <x:f>G37-H37</x:f>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L37" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:19">
+      <x:c r="B38" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G38" s="2">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="H38" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I38" s="2">
+        <x:f>G38-H38</x:f>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:19">
+      <x:c r="B39" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F39" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G39" s="2">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="H39" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I39" s="2">
+        <x:f>G39-H39</x:f>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L39" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:19">
+      <x:c r="B40" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G40" s="2">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="H40" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I40" s="2">
+        <x:f>G40-H40</x:f>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:19">
+      <x:c r="B41" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="F41" s="2">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G41" s="2">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="H41" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I41" s="2">
+        <x:f>G41-H41</x:f>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L41" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:19">
+      <x:c r="B42" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="F42" s="2">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G42" s="2">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="H42" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I42" s="2">
+        <x:f>G42-H42</x:f>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L42" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:19">
+      <x:c r="B43" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F43" s="2">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G43" s="2">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="H43" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I43" s="2">
+        <x:f>G43-H43</x:f>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:19">
+      <x:c r="B44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G44" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I44" s="2">
+        <x:f>-H44</x:f>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L44" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:19">
+      <x:c r="B45" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G45" s="2">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="H45" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I45" s="2">
+        <x:f>G45-H45</x:f>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:19">
+      <x:c r="B46" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="F46" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G46" s="2">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="H46" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I46" s="2">
+        <x:f>G46-H46</x:f>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L46" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:19">
+      <x:c r="B47" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="F47" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G47" s="2">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="H47" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I47" s="2">
+        <x:f>G47-H47</x:f>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L47" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:19">
+      <x:c r="B48" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G48" s="2">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="H48" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I48" s="2">
+        <x:f>G48-H48</x:f>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:19">
+      <x:c r="B49" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F49" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G49" s="2">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="H49" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I49" s="2">
+        <x:f>G49-H49</x:f>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L49" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:19">
+      <x:c r="B50" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G50" s="2">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="H50" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I50" s="2">
+        <x:f>G50-H50</x:f>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:19">
+      <x:c r="B51" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G51" s="2">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="H51" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I51" s="2">
+        <x:f>G51-H51</x:f>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:19">
+      <x:c r="B52" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="F52" s="2">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G52" s="2">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="H52" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I52" s="2">
+        <x:f>G52-H52</x:f>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L52" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:19">
+      <x:c r="B53" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="F53" s="2">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G53" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I53" s="2">
+        <x:f>-H53</x:f>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L53" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:19">
+      <x:c r="B54" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="F54" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G54" s="2">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="H54" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I54" s="2">
+        <x:f>G54-H54</x:f>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L54" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M54" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:19">
+      <x:c r="B55" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G55" s="2">
+        <x:v>2600</x:v>
+      </x:c>
+      <x:c r="H55" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" s="2">
+        <x:f>G55-H55</x:f>
+      </x:c>
+      <x:c r="J55" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L55" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="M55" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:19">
+      <x:c r="B56" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G56" s="2">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="H56" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I56" s="2">
+        <x:f>G56-H56</x:f>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L56" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:19">
+      <x:c r="B57" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G57" s="2">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="H57" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I57" s="2">
+        <x:f>G57-H57</x:f>
+      </x:c>
+      <x:c r="J57" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L57" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:19">
+      <x:c r="B58" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="F58" s="2">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G58" s="2">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="H58" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I58" s="2">
+        <x:f>G58-H58</x:f>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L58" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:19">
+      <x:c r="A59" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="F59" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G59" s="2">
+        <x:v>6900</x:v>
+      </x:c>
+      <x:c r="H59" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I59" s="2">
+        <x:f>G59-H59</x:f>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L59" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:19">
+      <x:c r="A60" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="F60" s="2">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G60" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I60" s="2">
+        <x:f>-H60</x:f>
+      </x:c>
+      <x:c r="J60" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L60" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:19">
+      <x:c r="A61" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G61" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I61" s="2">
+        <x:f>H61</x:f>
+      </x:c>
+      <x:c r="J61" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L61" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:19">
+      <x:c r="A62" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G62" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I62" s="2">
+        <x:f>H62</x:f>
+      </x:c>
+      <x:c r="J62" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L62" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:19">
+      <x:c r="A63" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G63" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I63" s="2">
+        <x:f>H63</x:f>
+      </x:c>
+      <x:c r="J63" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L63" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:19">
+      <x:c r="A64" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="F64" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G64" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I64" s="2">
+        <x:f>-H64</x:f>
+      </x:c>
+      <x:c r="J64" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L64" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:19">
+      <x:c r="A65" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G65" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="2">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I65" s="2">
+        <x:f>H65</x:f>
+      </x:c>
+      <x:c r="J65" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L65" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:19">
+      <x:c r="D67" s="3">
+        <x:f>COUNTA(D3:D65)</x:f>
+      </x:c>
+      <x:c r="G67" s="3">
+        <x:f>SUBTOTAL(9,G3:G65)</x:f>
+      </x:c>
+      <x:c r="H67" s="3">
+        <x:f>SUBTOTAL(9,H3:H65)</x:f>
+      </x:c>
+      <x:c r="I67" s="3">
+        <x:f>SUBTOTAL(9,I3:I65)</x:f>
+      </x:c>
+      <x:c r="J67" s="3">
+        <x:f>SUBTOTAL(9,J3:J65)</x:f>
+      </x:c>
+      <x:c r="K67" s="3">
+        <x:f>SUBTOTAL(9,K3:K65)</x:f>
+      </x:c>
+      <x:c r="L67" s="3">
+        <x:f>SUBTOTAL(9,L3:L65)</x:f>
+      </x:c>
+      <x:c r="M67" s="3">
+        <x:f>SUBTOTAL(9,M3:M65)</x:f>
+      </x:c>
+      <x:c r="N67" s="3">
+        <x:f>SUBTOTAL(9,N3:N65)</x:f>
+      </x:c>
+      <x:c r="O67" s="3">
+        <x:f>SUBTOTAL(9,O3:O65)</x:f>
+      </x:c>
+      <x:c r="P67" s="3">
+        <x:f>SUBTOTAL(9,P3:P65)</x:f>
+      </x:c>
+      <x:c r="Q67" s="3">
+        <x:f>SUBTOTAL(9,Q3:Q65)</x:f>
+      </x:c>
+      <x:c r="R67" s="3">
+        <x:f>SUBTOTAL(9,R3:R65)</x:f>
+      </x:c>
+      <x:c r="S67" s="3">
+        <x:f>SUBTOTAL(9,S3:S65)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:19">
+      <x:c r="A69" s="3" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C69" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E69" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="J69" s="9" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K69" s="9" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L69" s="9" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:19">
+      <x:c r="A70" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B70" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C70" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$69,L$3:L$65,A$70)</x:f>
+      </x:c>
+      <x:c r="E70" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$69,L$3:L$65,A$70)</x:f>
+      </x:c>
+      <x:c r="J70" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K70" s="0">
+        <x:f>SUMIFS(G$3:G$65,J$3:J$65,"An Tam")</x:f>
+      </x:c>
+      <x:c r="L70" s="0">
+        <x:f>COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"An Tam")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:19">
+      <x:c r="B71" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C71" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J71" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:19">
+      <x:c r="B72" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C72" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J72" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:19">
+      <x:c r="B73" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C73" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J73" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:19">
+      <x:c r="B74" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C74" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J74" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:19">
+      <x:c r="B75" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="K75" s="19">
+        <x:f>SUBTOTAL(9,K70:K74)</x:f>
+      </x:c>
+      <x:c r="L75" s="19">
+        <x:f>L70</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:19">
+      <x:c r="B76" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:19">
+      <x:c r="J77" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K77" s="9" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L77" s="9" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:19">
+      <x:c r="B78" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C78" s="3">
+        <x:f>SUBTOTAL(9,C70:C76)</x:f>
+      </x:c>
+      <x:c r="E78" s="3">
+        <x:f>E70</x:f>
+      </x:c>
+      <x:c r="J78" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K78" s="0">
+        <x:f>SUMIFS(G$3:G$65,J$3:J$65,"c.cuong")</x:f>
+      </x:c>
+      <x:c r="L78" s="0">
+        <x:f>COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.cuong")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:19">
+      <x:c r="J79" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="K79" s="0">
+        <x:f>-SUMIFS(H$3:H$65,J$3:J$65,"c.cuong")+COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.cuong")*5</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:19">
+      <x:c r="A80" s="3" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C80" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E80" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="J80" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="K80" s="0">
+        <x:f>-(COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.cuong")-COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.cuong",P$3:P$67,"xx"))*2</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:19">
+      <x:c r="A81" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B81" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C81" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$80,L$3:L$65,A$81)</x:f>
+      </x:c>
+      <x:c r="E81" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$80,L$3:L$65,A$81)</x:f>
+      </x:c>
+      <x:c r="J81" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:19">
+      <x:c r="B82" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C82" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:19">
+      <x:c r="B83" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C83" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="19">
+        <x:f>SUBTOTAL(9,K78:K82)</x:f>
+      </x:c>
+      <x:c r="L83" s="19">
+        <x:f>L78</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:19">
+      <x:c r="B84" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C84" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:19">
+      <x:c r="B85" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K85" s="9" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L85" s="9" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:19">
+      <x:c r="B86" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="J86" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K86" s="0">
+        <x:f>SUMIFS(G$3:G$65,J$3:J$65,"c.hieu")</x:f>
+      </x:c>
+      <x:c r="L86" s="0">
+        <x:f>COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.hieu")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:19">
+      <x:c r="B87" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="J87" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="K87" s="0">
+        <x:f>-SUMIFS(H$3:H$65,J$3:J$65,"c.hieu")+COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.hieu")*5</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:19">
+      <x:c r="J88" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="K88" s="0">
+        <x:f>-(COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.hieu")-COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"c.hieu",P$3:P$67,"xx"))*2</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:19">
+      <x:c r="B89" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C89" s="3">
+        <x:f>SUBTOTAL(9,C81:C87)</x:f>
+      </x:c>
+      <x:c r="E89" s="3">
+        <x:f>E81</x:f>
+      </x:c>
+      <x:c r="J89" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:19">
+      <x:c r="J90" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:19">
+      <x:c r="A91" s="3" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C91" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E91" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="K91" s="19">
+        <x:f>SUBTOTAL(9,K86:K90)</x:f>
+      </x:c>
+      <x:c r="L91" s="19">
+        <x:f>L86</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:19">
+      <x:c r="A92" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B92" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C92" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$91,L$3:L$65,A$92)</x:f>
+      </x:c>
+      <x:c r="E92" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$91,L$3:L$65,A$92)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:19">
+      <x:c r="B93" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C93" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J93" s="9" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K93" s="9" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L93" s="9" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:19">
+      <x:c r="B94" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C94" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J94" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K94" s="0">
+        <x:f>SUMIFS(G$3:G$65,J$3:J$65,"a.quyen")</x:f>
+      </x:c>
+      <x:c r="L94" s="0">
+        <x:f>COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"a.quyen")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:19">
+      <x:c r="B95" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C95" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J95" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="K95" s="0">
+        <x:f>-SUMIFS(H$3:H$65,J$3:J$65,"a.quyen")+COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"a.quyen")*5</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:19">
+      <x:c r="B96" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J96" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="K96" s="0">
+        <x:f>-(COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"a.quyen")-COUNTIFS(B$3:B$65,"&lt;&gt;",J$3:J$65,"a.quyen",P$3:P$67,"xx"))*2</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:19">
+      <x:c r="B97" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="J97" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:19">
+      <x:c r="B98" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="J98" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:19">
+      <x:c r="K99" s="19">
+        <x:f>SUBTOTAL(9,K94:K98)</x:f>
+      </x:c>
+      <x:c r="L99" s="19">
+        <x:f>L94</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:19">
+      <x:c r="B100" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C100" s="3">
+        <x:f>SUBTOTAL(9,C92:C98)</x:f>
+      </x:c>
+      <x:c r="E100" s="3">
+        <x:f>E92</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:19">
+      <x:c r="A102" s="3" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C102" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E102" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:19">
+      <x:c r="A103" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B103" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C103" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$102,L$3:L$65,A$103)</x:f>
+      </x:c>
+      <x:c r="E103" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$102,L$3:L$65,A$103)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:19">
+      <x:c r="B104" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C104" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:19">
+      <x:c r="B105" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C105" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:19">
+      <x:c r="B106" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C106" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:19">
+      <x:c r="B107" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C107" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:19">
+      <x:c r="B108" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:19">
+      <x:c r="B109" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:19">
+      <x:c r="B111" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C111" s="3">
+        <x:f>SUBTOTAL(9,C103:C109)</x:f>
+      </x:c>
+      <x:c r="E111" s="3">
+        <x:f>E103</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:19">
+      <x:c r="A113" s="3" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C113" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E113" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:19">
+      <x:c r="A114" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B114" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C114" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$113,L$3:L$65,A$114)</x:f>
+      </x:c>
+      <x:c r="E114" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$113,L$3:L$65,A$114)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:19">
+      <x:c r="B115" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C115" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:19">
+      <x:c r="B116" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C116" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:19">
+      <x:c r="B117" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C117" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:19">
+      <x:c r="B118" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:19">
+      <x:c r="B119" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:19">
+      <x:c r="B120" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:19">
+      <x:c r="B122" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C122" s="3">
+        <x:f>SUBTOTAL(9,C114:C120)</x:f>
+      </x:c>
+      <x:c r="E122" s="3">
+        <x:f>E114</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:19">
+      <x:c r="A124" s="3" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C124" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E124" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:19">
+      <x:c r="A125" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B125" s="29" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="C125" s="29">
+        <x:f>SUMIFS(I$3:I$65,B$3:B$65,B$124,L$3:L$65,A$125)</x:f>
+      </x:c>
+      <x:c r="E125" s="29">
+        <x:f>COUNTIFS(B$3:B$65,B$124,L$3:L$65,A$125)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:19">
+      <x:c r="B126" s="17" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C126" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:19">
+      <x:c r="B127" s="17" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C127" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:19">
+      <x:c r="B128" s="17" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C128" s="17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:19">
+      <x:c r="B129" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C129" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:19">
+      <x:c r="B130" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:19">
+      <x:c r="B131" s="30" t="s">
+        <x:v>463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:19">
+      <x:c r="B133" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C133" s="3">
+        <x:f>SUBTOTAL(9,C125:C131)</x:f>
+      </x:c>
+      <x:c r="E133" s="3">
+        <x:f>E125</x:f>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A2:P65"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F84371A-0E82-4EF7-BAB3-93969EFB27EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6509C32C-DEA3-4920-A935-5CA17101B337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
+    <workbookView xWindow="-28920" yWindow="-150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
   </bookViews>
   <sheets>
     <sheet name="02-03" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="662">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2023,6 +2023,15 @@
   </si>
   <si>
     <t>at  11-03</t>
+  </si>
+  <si>
+    <t>HD000681</t>
+  </si>
+  <si>
+    <t>hy hy</t>
+  </si>
+  <si>
+    <t>trả shop</t>
   </si>
 </sst>
 </file>
@@ -2032,7 +2041,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]General"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2102,6 +2111,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2417,7 +2433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2563,6 +2579,10 @@
     <xf numFmtId="164" fontId="4" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2898,24 +2918,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="54.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="87.5703125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="54.375" customWidth="1"/>
+    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="87.625" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="4.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2968,7 +2988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -3001,7 +3021,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -3040,7 +3060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -3076,7 +3096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -3112,7 +3132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -3145,7 +3165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -3181,7 +3201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -3214,7 +3234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -3247,7 +3267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -3283,7 +3303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -3316,7 +3336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -3349,7 +3369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -3382,7 +3402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -3418,7 +3438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -3451,7 +3471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -3487,7 +3507,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -3520,7 +3540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -3553,7 +3573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -3586,7 +3606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -3619,7 +3639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -3652,7 +3672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -3688,7 +3708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -3724,7 +3744,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -3757,7 +3777,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>16</v>
       </c>
@@ -3790,7 +3810,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>16</v>
       </c>
@@ -3823,7 +3843,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>16</v>
       </c>
@@ -3859,7 +3879,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>16</v>
       </c>
@@ -3895,7 +3915,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>16</v>
       </c>
@@ -3931,7 +3951,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>16</v>
       </c>
@@ -3967,7 +3987,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>16</v>
       </c>
@@ -4000,7 +4020,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>16</v>
       </c>
@@ -4036,7 +4056,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>16</v>
       </c>
@@ -4072,7 +4092,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>16</v>
       </c>
@@ -4108,7 +4128,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>16</v>
       </c>
@@ -4141,7 +4161,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>16</v>
       </c>
@@ -4174,7 +4194,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>16</v>
       </c>
@@ -4207,7 +4227,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>16</v>
       </c>
@@ -4240,7 +4260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>16</v>
       </c>
@@ -4273,7 +4293,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>16</v>
       </c>
@@ -4309,7 +4329,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>16</v>
       </c>
@@ -4345,7 +4365,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>16</v>
       </c>
@@ -4381,7 +4401,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>16</v>
       </c>
@@ -4414,7 +4434,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>16</v>
       </c>
@@ -4450,7 +4470,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>16</v>
       </c>
@@ -4483,7 +4503,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>16</v>
       </c>
@@ -4519,7 +4539,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>16</v>
       </c>
@@ -4552,7 +4572,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>16</v>
       </c>
@@ -4588,7 +4608,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>16</v>
       </c>
@@ -4624,7 +4644,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>16</v>
       </c>
@@ -4657,7 +4677,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>16</v>
       </c>
@@ -4690,7 +4710,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>16</v>
       </c>
@@ -4723,7 +4743,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>16</v>
       </c>
@@ -4759,7 +4779,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>16</v>
       </c>
@@ -4795,7 +4815,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>16</v>
       </c>
@@ -4831,7 +4851,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>16</v>
       </c>
@@ -4864,7 +4884,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>16</v>
       </c>
@@ -4897,7 +4917,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>16</v>
       </c>
@@ -4930,7 +4950,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>16</v>
       </c>
@@ -4963,7 +4983,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>16</v>
       </c>
@@ -4999,7 +5019,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>16</v>
       </c>
@@ -5035,7 +5055,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>16</v>
       </c>
@@ -5071,7 +5091,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>16</v>
       </c>
@@ -5104,7 +5124,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>16</v>
       </c>
@@ -5140,7 +5160,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>16</v>
       </c>
@@ -5173,7 +5193,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>16</v>
       </c>
@@ -5206,7 +5226,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>16</v>
       </c>
@@ -5242,7 +5262,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>16</v>
       </c>
@@ -5278,7 +5298,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
         <v>16</v>
       </c>
@@ -5314,7 +5334,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>16</v>
       </c>
@@ -5350,7 +5370,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
         <v>16</v>
       </c>
@@ -5383,7 +5403,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>16</v>
       </c>
@@ -5419,7 +5439,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>16</v>
       </c>
@@ -5455,7 +5475,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>253</v>
       </c>
@@ -5488,7 +5508,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>253</v>
       </c>
@@ -5524,7 +5544,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>253</v>
       </c>
@@ -5560,7 +5580,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>253</v>
       </c>
@@ -5636,7 +5656,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="8"/>
       <c r="B83" s="9" t="s">
         <v>265</v>
@@ -5661,7 +5681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="8"/>
       <c r="B84" s="9" t="s">
         <v>267</v>
@@ -5679,7 +5699,7 @@
         <v>-335</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="8"/>
       <c r="B85" s="12" t="s">
         <v>269</v>
@@ -5704,7 +5724,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="8"/>
       <c r="B87" s="12" t="s">
         <v>271</v>
@@ -5755,7 +5775,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J91" t="s">
         <v>266</v>
       </c>
@@ -5768,7 +5788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J92" t="s">
         <v>268</v>
       </c>
@@ -5777,12 +5797,12 @@
         <v>-590</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J94" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J95" s="2" t="s">
         <v>272</v>
       </c>
@@ -5808,7 +5828,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J99" t="s">
         <v>266</v>
       </c>
@@ -5821,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J100" t="s">
         <v>268</v>
       </c>
@@ -5830,12 +5850,12 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="102" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J102" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="103" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J103" s="2" t="s">
         <v>272</v>
       </c>
@@ -5858,16 +5878,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.875" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.375" customWidth="1"/>
+    <col min="6" max="6" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.125" customWidth="1"/>
+    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5929,7 +5949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="47" t="s">
         <v>16</v>
       </c>
@@ -5968,7 +5988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="47" t="s">
         <v>16</v>
       </c>
@@ -6013,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="47" t="s">
         <v>16</v>
       </c>
@@ -6052,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="47" t="s">
         <v>16</v>
       </c>
@@ -6091,7 +6111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="47" t="s">
         <v>16</v>
       </c>
@@ -6130,7 +6150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="47" t="s">
         <v>16</v>
       </c>
@@ -6169,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="47" t="s">
         <v>16</v>
       </c>
@@ -6208,7 +6228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="47" t="s">
         <v>16</v>
       </c>
@@ -6247,7 +6267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="47" t="s">
         <v>16</v>
       </c>
@@ -6286,7 +6306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="47" t="s">
         <v>16</v>
       </c>
@@ -6328,7 +6348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="47" t="s">
         <v>16</v>
       </c>
@@ -6367,7 +6387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="47" t="s">
         <v>16</v>
       </c>
@@ -6406,7 +6426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="47" t="s">
         <v>16</v>
       </c>
@@ -6448,7 +6468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="47" t="s">
         <v>16</v>
       </c>
@@ -6487,7 +6507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="47" t="s">
         <v>16</v>
       </c>
@@ -6529,7 +6549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="47" t="s">
         <v>16</v>
       </c>
@@ -6568,7 +6588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="47" t="s">
         <v>16</v>
       </c>
@@ -6607,7 +6627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="47" t="s">
         <v>16</v>
       </c>
@@ -6646,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="47" t="s">
         <v>16</v>
       </c>
@@ -6685,7 +6705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="47" t="s">
         <v>16</v>
       </c>
@@ -6724,7 +6744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="47" t="s">
         <v>16</v>
       </c>
@@ -6763,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="47" t="s">
         <v>16</v>
       </c>
@@ -6802,7 +6822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="47" t="s">
         <v>16</v>
       </c>
@@ -6841,7 +6861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="47" t="s">
         <v>16</v>
       </c>
@@ -6883,7 +6903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="47" t="s">
         <v>16</v>
       </c>
@@ -6925,7 +6945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="47" t="s">
         <v>16</v>
       </c>
@@ -6964,7 +6984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="47" t="s">
         <v>16</v>
       </c>
@@ -7003,7 +7023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="47" t="s">
         <v>16</v>
       </c>
@@ -7045,7 +7065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="47" t="s">
         <v>16</v>
       </c>
@@ -7087,7 +7107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="47" t="s">
         <v>16</v>
       </c>
@@ -7129,7 +7149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="47" t="s">
         <v>16</v>
       </c>
@@ -7168,7 +7188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="47" t="s">
         <v>16</v>
       </c>
@@ -7207,7 +7227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="47" t="s">
         <v>16</v>
       </c>
@@ -7246,7 +7266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="47" t="s">
         <v>16</v>
       </c>
@@ -7285,7 +7305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="47" t="s">
         <v>16</v>
       </c>
@@ -7324,7 +7344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="47" t="s">
         <v>16</v>
       </c>
@@ -7363,7 +7383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="47" t="s">
         <v>16</v>
       </c>
@@ -7402,7 +7422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="47" t="s">
         <v>16</v>
       </c>
@@ -7441,7 +7461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="47" t="s">
         <v>16</v>
       </c>
@@ -7483,7 +7503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="47" t="s">
         <v>16</v>
       </c>
@@ -7522,7 +7542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="47" t="s">
         <v>16</v>
       </c>
@@ -7561,7 +7581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="47" t="s">
         <v>16</v>
       </c>
@@ -7600,7 +7620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="47" t="s">
         <v>16</v>
       </c>
@@ -7639,7 +7659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="47" t="s">
         <v>16</v>
       </c>
@@ -7678,7 +7698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="47" t="s">
         <v>16</v>
       </c>
@@ -7717,7 +7737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="47" t="s">
         <v>16</v>
       </c>
@@ -7759,7 +7779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="47" t="s">
         <v>16</v>
       </c>
@@ -7798,7 +7818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="47" t="s">
         <v>16</v>
       </c>
@@ -7837,7 +7857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="47" t="s">
         <v>16</v>
       </c>
@@ -7876,7 +7896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="47" t="s">
         <v>16</v>
       </c>
@@ -7915,7 +7935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="47" t="s">
         <v>16</v>
       </c>
@@ -7954,7 +7974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="47" t="s">
         <v>16</v>
       </c>
@@ -7993,7 +8013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="47" t="s">
         <v>16</v>
       </c>
@@ -8032,7 +8052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="52"/>
       <c r="B56" s="52" t="s">
         <v>16</v>
@@ -8082,7 +8102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B57" s="47" t="s">
         <v>16</v>
       </c>
@@ -8121,7 +8141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B58" s="47" t="s">
         <v>16</v>
       </c>
@@ -8160,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B59" s="47" t="s">
         <v>16</v>
       </c>
@@ -8199,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="47" t="s">
         <v>253</v>
       </c>
@@ -8241,7 +8261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="47" t="s">
         <v>253</v>
       </c>
@@ -8283,7 +8303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="47" t="s">
         <v>253</v>
       </c>
@@ -8325,7 +8345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="47" t="s">
         <v>253</v>
       </c>
@@ -8367,7 +8387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47" t="s">
         <v>253</v>
       </c>
@@ -8409,7 +8429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="47" t="s">
         <v>253</v>
       </c>
@@ -8451,7 +8471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="47" t="s">
         <v>253</v>
       </c>
@@ -8493,7 +8513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G69">
         <f>SUBTOTAL(9,G3:G66)</f>
         <v>35905</v>
@@ -8539,7 +8559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="H70">
         <f>-11*17</f>
         <v>-187</v>
@@ -8813,7 +8833,7 @@
       <c r="P78" s="18"/>
       <c r="Q78" s="18"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K79" s="17" t="s">
         <v>25</v>
       </c>
@@ -8876,7 +8896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K87" s="17" t="s">
         <v>20</v>
       </c>
@@ -8939,7 +8959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K95" s="17" t="s">
         <v>281</v>
       </c>
@@ -9021,28 +9041,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:S82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="60.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="29.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="39.125" customWidth="1"/>
+    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="60.375" customWidth="1"/>
+    <col min="6" max="6" width="9.875" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="10.75" customWidth="1"/>
+    <col min="13" max="13" width="29.75" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -9101,7 +9121,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -9140,7 +9160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -9179,7 +9199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -9218,7 +9238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -9257,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -9296,7 +9316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -9335,7 +9355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -9374,7 +9394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -9413,7 +9433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -9452,7 +9472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -9491,7 +9511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -9530,7 +9550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -9569,7 +9589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -9608,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -9647,7 +9667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -9686,7 +9706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -9725,7 +9745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -9767,7 +9787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -9806,7 +9826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -9845,7 +9865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -9884,7 +9904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -9923,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -9962,7 +9982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -10001,7 +10021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>16</v>
       </c>
@@ -10040,7 +10060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>16</v>
       </c>
@@ -10079,7 +10099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>16</v>
       </c>
@@ -10118,7 +10138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>16</v>
       </c>
@@ -10157,7 +10177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>16</v>
       </c>
@@ -10196,7 +10216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>16</v>
       </c>
@@ -10244,7 +10264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>16</v>
       </c>
@@ -10292,7 +10312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>16</v>
       </c>
@@ -10340,7 +10360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>16</v>
       </c>
@@ -10388,7 +10408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>16</v>
       </c>
@@ -10427,7 +10447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>16</v>
       </c>
@@ -10466,7 +10486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>253</v>
       </c>
@@ -10505,7 +10525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>253</v>
       </c>
@@ -10547,7 +10567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>253</v>
       </c>
@@ -10589,7 +10609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>253</v>
       </c>
@@ -10631,7 +10651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="D42" s="1">
         <f>COUNTA(D3:D40)</f>
         <v>34</v>
@@ -10689,7 +10709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>574</v>
       </c>
@@ -10715,7 +10735,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>481</v>
       </c>
@@ -10749,7 +10769,7 @@
         <v>3457</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>466</v>
       </c>
@@ -10779,7 +10799,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>269</v>
       </c>
@@ -10808,7 +10828,7 @@
         <v>9234</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
         <v>270</v>
       </c>
@@ -10831,7 +10851,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>471</v>
       </c>
@@ -10846,7 +10866,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B50" s="69" t="s">
         <v>273</v>
       </c>
@@ -10866,7 +10886,7 @@
         <v>-15925</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="O51" s="4" t="s">
         <v>473</v>
       </c>
@@ -10875,7 +10895,7 @@
         <v>3467</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>274</v>
       </c>
@@ -10896,7 +10916,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J53" t="s">
         <v>266</v>
       </c>
@@ -10909,7 +10929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>578</v>
       </c>
@@ -10933,7 +10953,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>282</v>
       </c>
@@ -10958,7 +10978,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>466</v>
       </c>
@@ -10974,7 +10994,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>269</v>
       </c>
@@ -10990,7 +11010,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
         <v>270</v>
       </c>
@@ -11011,12 +11031,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B60" s="69" t="s">
         <v>273</v>
       </c>
@@ -11030,7 +11050,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J61" t="s">
         <v>266</v>
       </c>
@@ -11043,7 +11063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>274</v>
       </c>
@@ -11065,7 +11085,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J63" t="s">
         <v>468</v>
       </c>
@@ -11076,17 +11096,17 @@
         <v>582</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J64" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J65" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="66" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="10:12" ht="15" x14ac:dyDescent="0.25">
       <c r="K66" s="42">
         <f>SUBTOTAL(9,K61:K65)</f>
         <v>9234</v>
@@ -11096,7 +11116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="10:12" ht="15" x14ac:dyDescent="0.25">
       <c r="J68" s="40" t="s">
         <v>239</v>
       </c>
@@ -11107,7 +11127,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J69" t="s">
         <v>266</v>
       </c>
@@ -11120,7 +11140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J70" t="s">
         <v>268</v>
       </c>
@@ -11132,7 +11152,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="71" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J71" t="s">
         <v>468</v>
       </c>
@@ -11143,17 +11163,17 @@
         <v>584</v>
       </c>
     </row>
-    <row r="72" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J72" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J73" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="74" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="10:12" ht="15" x14ac:dyDescent="0.25">
       <c r="K74" s="42">
         <f>SUBTOTAL(9,K69:K73)</f>
         <v>1396</v>
@@ -11163,7 +11183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="10:12" ht="15" x14ac:dyDescent="0.25">
       <c r="J76" s="40" t="s">
         <v>438</v>
       </c>
@@ -11174,7 +11194,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J77" t="s">
         <v>266</v>
       </c>
@@ -11187,7 +11207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J78" t="s">
         <v>268</v>
       </c>
@@ -11199,7 +11219,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="79" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J79" t="s">
         <v>468</v>
       </c>
@@ -11210,7 +11230,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="80" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J80" s="2" t="s">
         <v>72</v>
       </c>
@@ -11221,12 +11241,12 @@
         <v>587</v>
       </c>
     </row>
-    <row r="81" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J81" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="82" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="10:12" ht="15" x14ac:dyDescent="0.25">
       <c r="K82" s="42">
         <f>SUBTOTAL(9,K77:K81)</f>
         <v>-5</v>
@@ -11245,28 +11265,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A48BAE-53B9-4A6C-8EE1-181979E337EB}">
   <dimension ref="A1:Q75"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="60.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="29.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="39.125" customWidth="1"/>
+    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="60.375" customWidth="1"/>
+    <col min="6" max="6" width="9.875" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="10.75" customWidth="1"/>
+    <col min="13" max="13" width="29.75" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>588</v>
       </c>
@@ -11274,7 +11294,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -11327,7 +11347,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -11366,7 +11386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -11405,7 +11425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -11444,7 +11464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -11483,7 +11503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -11522,7 +11542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -11561,7 +11581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -11600,7 +11620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -11639,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -11678,7 +11698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -11717,7 +11737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -11756,7 +11776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -11795,7 +11815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -11834,7 +11854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -11873,7 +11893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -11912,7 +11932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -11951,7 +11971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -11993,7 +12013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -12032,7 +12052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -12071,7 +12091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -12110,7 +12130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -12149,7 +12169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -12188,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -12227,7 +12247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>16</v>
       </c>
@@ -12266,7 +12286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>16</v>
       </c>
@@ -12305,7 +12325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>16</v>
       </c>
@@ -12344,7 +12364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>16</v>
       </c>
@@ -12383,7 +12403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>16</v>
       </c>
@@ -12422,7 +12442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>16</v>
       </c>
@@ -12470,7 +12490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>16</v>
       </c>
@@ -12518,7 +12538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>16</v>
       </c>
@@ -12566,7 +12586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>16</v>
       </c>
@@ -12614,7 +12634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>16</v>
       </c>
@@ -12653,7 +12673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>16</v>
       </c>
@@ -12692,7 +12712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>253</v>
       </c>
@@ -12731,7 +12751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>253</v>
       </c>
@@ -12773,7 +12793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>253</v>
       </c>
@@ -12815,7 +12835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>253</v>
       </c>
@@ -12857,7 +12877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G43">
         <f t="shared" ref="G43:Q43" si="1">SUBTOTAL(9,G3:G40)</f>
         <v>23700</v>
@@ -13159,7 +13179,7 @@
       <c r="P52" s="18"/>
       <c r="Q52" s="18"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K53" s="17" t="s">
         <v>25</v>
       </c>
@@ -13222,7 +13242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K61" s="17" t="s">
         <v>20</v>
       </c>
@@ -13285,7 +13305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K69" s="17" t="s">
         <v>485</v>
       </c>
@@ -13367,28 +13387,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECFBA487-CF78-4B18-9BFE-7F26F31E27D9}">
   <dimension ref="A2:Q59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="49.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="49.125" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="10.75" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="11.125" customWidth="1"/>
+    <col min="16" max="16" width="4.875" customWidth="1"/>
+    <col min="17" max="17" width="6.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -13441,7 +13461,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -13480,7 +13500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -13519,7 +13539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -13558,7 +13578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -13597,7 +13617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -13636,7 +13656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -13675,7 +13695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -13714,7 +13734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -13753,7 +13773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -13792,7 +13812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -13831,7 +13851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -13870,7 +13890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -13909,7 +13929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -13951,7 +13971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -13990,7 +14010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -14029,7 +14049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -14068,7 +14088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -14107,7 +14127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -14146,7 +14166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -14191,7 +14211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -14230,7 +14250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -14269,7 +14289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>253</v>
       </c>
@@ -14311,7 +14331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -14362,7 +14382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="D27" s="1">
         <f>COUNTA(D3:D25)</f>
         <v>22</v>
@@ -14412,7 +14432,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -14436,7 +14456,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>595</v>
       </c>
@@ -14474,7 +14494,7 @@
         <v>5055</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>466</v>
       </c>
@@ -14506,7 +14526,7 @@
         <v>3305</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>269</v>
       </c>
@@ -14530,7 +14550,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
         <v>270</v>
       </c>
@@ -14554,7 +14574,7 @@
         <v>9545</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>471</v>
       </c>
@@ -14571,7 +14591,7 @@
         <v>-18155</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="69" t="s">
         <v>273</v>
       </c>
@@ -14593,7 +14613,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>274</v>
       </c>
@@ -14615,7 +14635,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K38" t="s">
         <v>266</v>
       </c>
@@ -14628,7 +14648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K39" t="s">
         <v>268</v>
       </c>
@@ -14641,22 +14661,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K40" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K41" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K42" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="L43" s="42">
         <f>SUBTOTAL(9,L38:L42)</f>
         <v>3305</v>
@@ -14666,7 +14686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="K45" s="40" t="s">
         <v>239</v>
       </c>
@@ -14677,7 +14697,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K46" t="s">
         <v>266</v>
       </c>
@@ -14690,7 +14710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K47" t="s">
         <v>268</v>
       </c>
@@ -14703,22 +14723,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K48" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K49" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K50" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="L51" s="42">
         <f>SUBTOTAL(9,L46:L50)</f>
         <v>795</v>
@@ -14728,7 +14748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="K53" s="40" t="s">
         <v>638</v>
       </c>
@@ -14739,7 +14759,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K54" t="s">
         <v>266</v>
       </c>
@@ -14752,7 +14772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K55" t="s">
         <v>268</v>
       </c>
@@ -14765,22 +14785,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K56" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K57" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K58" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="L59" s="42">
         <f>SUBTOTAL(9,L54:L58)</f>
         <v>9545</v>
@@ -14809,28 +14829,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:Q59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="49.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="49.125" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="10.75" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="11.125" customWidth="1"/>
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+    <col min="17" max="17" width="6.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -14883,7 +14903,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -14896,7 +14916,7 @@
       <c r="E3" t="s">
         <v>594</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="91" t="s">
         <v>95</v>
       </c>
       <c r="G3" s="7">
@@ -14922,7 +14942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -14935,7 +14955,7 @@
       <c r="E4" t="s">
         <v>598</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="91">
         <v>7</v>
       </c>
       <c r="G4" s="7">
@@ -14957,24 +14977,27 @@
       <c r="L4" t="s">
         <v>595</v>
       </c>
+      <c r="M4" t="s">
+        <v>312</v>
+      </c>
       <c r="Q4" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>599</v>
+      <c r="C5" s="17" t="s">
+        <v>660</v>
       </c>
       <c r="D5" t="s">
-        <v>600</v>
+        <v>659</v>
       </c>
       <c r="E5" t="s">
         <v>601</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="91">
         <v>10</v>
       </c>
       <c r="G5" s="7">
@@ -15000,7 +15023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -15013,7 +15036,7 @@
       <c r="E6" t="s">
         <v>604</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="91">
         <v>4</v>
       </c>
       <c r="G6" s="7">
@@ -15039,7 +15062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -15052,7 +15075,7 @@
       <c r="E7" t="s">
         <v>607</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="91" t="s">
         <v>91</v>
       </c>
       <c r="G7" s="7">
@@ -15078,7 +15101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -15091,7 +15114,7 @@
       <c r="E8" t="s">
         <v>610</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="91">
         <v>9</v>
       </c>
       <c r="G8" s="7">
@@ -15117,7 +15140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -15130,7 +15153,7 @@
       <c r="E9" t="s">
         <v>613</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="91" t="s">
         <v>95</v>
       </c>
       <c r="G9" s="7">
@@ -15156,7 +15179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -15169,7 +15192,7 @@
       <c r="E10" t="s">
         <v>616</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="91" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="7">
@@ -15195,7 +15218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -15208,7 +15231,7 @@
       <c r="E11" t="s">
         <v>619</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="91">
         <v>2</v>
       </c>
       <c r="G11" s="7">
@@ -15234,7 +15257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -15247,7 +15270,7 @@
       <c r="E12" t="s">
         <v>622</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="91" t="s">
         <v>51</v>
       </c>
       <c r="G12" s="7">
@@ -15273,7 +15296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -15286,7 +15309,7 @@
       <c r="E13" t="s">
         <v>625</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="91" t="s">
         <v>116</v>
       </c>
       <c r="G13" s="7">
@@ -15312,7 +15335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -15325,7 +15348,7 @@
       <c r="E14" t="s">
         <v>628</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="91" t="s">
         <v>91</v>
       </c>
       <c r="G14" s="7">
@@ -15351,7 +15374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -15364,11 +15387,11 @@
       <c r="E15" t="s">
         <v>631</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="91">
         <v>2</v>
       </c>
       <c r="G15" s="7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" s="7">
         <v>30</v>
@@ -15393,7 +15416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -15406,7 +15429,7 @@
       <c r="E16" t="s">
         <v>634</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="91">
         <v>4</v>
       </c>
       <c r="G16" s="7">
@@ -15432,7 +15455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -15445,14 +15468,14 @@
       <c r="E17" t="s">
         <v>637</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="91" t="s">
         <v>47</v>
       </c>
       <c r="G17" s="7">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="H17" s="7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="7">
         <f>G17-H17</f>
@@ -15471,7 +15494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -15484,14 +15507,14 @@
       <c r="E18" t="s">
         <v>641</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="91">
         <v>7</v>
       </c>
       <c r="G18" s="7">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="H18" s="7">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I18" s="7">
         <f>G18-H18</f>
@@ -15510,7 +15533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -15523,7 +15546,7 @@
       <c r="E19" t="s">
         <v>643</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="91">
         <v>10</v>
       </c>
       <c r="G19" s="7">
@@ -15549,7 +15572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -15562,14 +15585,14 @@
       <c r="E20" t="s">
         <v>645</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="91">
         <v>8</v>
       </c>
       <c r="G20" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H20" s="7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I20" s="7">
         <f>G20-H20</f>
@@ -15588,52 +15611,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
+    <row r="21" spans="1:17" s="92" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="92" t="s">
         <v>646</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="92" t="s">
         <v>647</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="92" t="s">
         <v>648</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="7">
-        <v>515</v>
-      </c>
-      <c r="H21" s="7">
-        <v>25</v>
-      </c>
-      <c r="I21" s="7">
+      <c r="G21" s="94">
+        <v>490</v>
+      </c>
+      <c r="H21" s="94">
+        <v>0</v>
+      </c>
+      <c r="I21" s="94">
         <f>G21-H21</f>
         <v>490</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="92" t="s">
         <v>438</v>
       </c>
-      <c r="K21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="K21" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="92" t="s">
         <v>595</v>
       </c>
-      <c r="N21" t="s">
+      <c r="M21" s="92" t="s">
+        <v>661</v>
+      </c>
+      <c r="N21" s="92" t="s">
         <v>288</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="92" t="s">
         <v>440</v>
       </c>
-      <c r="Q21" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q21" s="94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -15646,18 +15672,18 @@
       <c r="E22" t="s">
         <v>651</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="91" t="s">
         <v>47</v>
       </c>
       <c r="G22" s="7">
         <v>0</v>
       </c>
       <c r="H22" s="7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I22" s="7">
         <f>-H22</f>
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="J22" t="s">
         <v>638</v>
@@ -15672,7 +15698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -15685,7 +15711,7 @@
       <c r="E23" t="s">
         <v>654</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="91" t="s">
         <v>95</v>
       </c>
       <c r="G23" s="7">
@@ -15711,7 +15737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>253</v>
       </c>
@@ -15724,14 +15750,14 @@
       <c r="E24" t="s">
         <v>656</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="91" t="s">
         <v>61</v>
       </c>
       <c r="G24" s="7">
-        <v>7817</v>
+        <v>7850</v>
       </c>
       <c r="H24" s="7">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I24" s="7">
         <f>G24-H24</f>
@@ -15753,7 +15779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -15766,14 +15792,14 @@
       <c r="E25" t="s">
         <v>400</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="91" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="7">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="H25" s="7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I25" s="7">
         <f>G25-H25</f>
@@ -15804,22 +15830,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="D27" s="1">
         <f>COUNTA(D3:D25)</f>
         <v>22</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" ref="G27:Q27" si="1">SUBTOTAL(9,G3:G25)</f>
-        <v>20086</v>
+        <v>20120</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="1"/>
-        <v>19530</v>
+        <v>19525</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="1"/>
@@ -15854,7 +15880,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -15878,7 +15904,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>595</v>
       </c>
@@ -15887,7 +15913,7 @@
       </c>
       <c r="C30" s="73">
         <f>SUMIFS(G$3:G$25,B$3:B$25,A$29,L$3:L$25,A$30)</f>
-        <v>19616</v>
+        <v>19680</v>
       </c>
       <c r="D30" s="73"/>
       <c r="E30" s="3">
@@ -15902,7 +15928,7 @@
       </c>
       <c r="L30">
         <f>SUMIFS(G$3:G$25,J$3:J$25,K$29)</f>
-        <v>5195</v>
+        <v>5225</v>
       </c>
       <c r="M30">
         <f>SUMIFS(Q$3:Q$25,J$3:J$25,K$29)</f>
@@ -15913,16 +15939,16 @@
       </c>
       <c r="P30">
         <f>L35</f>
-        <v>5055</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>466</v>
       </c>
       <c r="C31" s="74">
         <f>-SUMIFS(H$3:H$25,B$3:B$25,A$29,L$3:L$25,A$30)</f>
-        <v>-526</v>
+        <v>-565</v>
       </c>
       <c r="D31" s="74"/>
       <c r="E31">
@@ -15948,7 +15974,7 @@
         <v>3305</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>269</v>
       </c>
@@ -15972,13 +15998,13 @@
         <v>795</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
         <v>270</v>
       </c>
       <c r="C33" s="72">
         <f>SUBTOTAL(9,C30:C32)</f>
-        <v>18160</v>
+        <v>18185</v>
       </c>
       <c r="D33" s="72"/>
       <c r="E33">
@@ -15993,10 +16019,10 @@
       </c>
       <c r="P33">
         <f>L59</f>
-        <v>9550</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+        <v>9545</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>471</v>
       </c>
@@ -16010,10 +16036,10 @@
       </c>
       <c r="P34">
         <f>-C37</f>
-        <v>-18160</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+        <v>-18185</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="69" t="s">
         <v>273</v>
       </c>
@@ -16021,7 +16047,7 @@
       <c r="D35" s="70"/>
       <c r="L35" s="42">
         <f>SUBTOTAL(9,L30:L34)</f>
-        <v>5055</v>
+        <v>5085</v>
       </c>
       <c r="M35" s="42">
         <f>M30</f>
@@ -16035,13 +16061,13 @@
         <v>545</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C37" s="71">
         <f>C33+C34+C35</f>
-        <v>18160</v>
+        <v>18185</v>
       </c>
       <c r="D37" s="71"/>
       <c r="E37" s="1" t="s">
@@ -16057,7 +16083,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K38" t="s">
         <v>266</v>
       </c>
@@ -16070,7 +16096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K39" t="s">
         <v>268</v>
       </c>
@@ -16083,22 +16109,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K40" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K41" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K42" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="L43" s="42">
         <f>SUBTOTAL(9,L38:L42)</f>
         <v>3305</v>
@@ -16108,7 +16134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="K45" s="40" t="s">
         <v>239</v>
       </c>
@@ -16119,7 +16145,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K46" t="s">
         <v>266</v>
       </c>
@@ -16132,7 +16158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K47" t="s">
         <v>268</v>
       </c>
@@ -16145,22 +16171,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K48" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K49" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K50" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="L51" s="42">
         <f>SUBTOTAL(9,L46:L50)</f>
         <v>795</v>
@@ -16170,7 +16196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="K53" s="40" t="s">
         <v>638</v>
       </c>
@@ -16181,51 +16207,51 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K54" t="s">
         <v>266</v>
       </c>
       <c r="L54">
         <f>SUMIFS(G$3:G$25,J$3:J$25,K$53)</f>
-        <v>9626</v>
+        <v>9685</v>
       </c>
       <c r="M54">
         <f>SUMIFS(Q$3:Q$25,J$3:J$25,K$53)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K55" t="s">
         <v>268</v>
       </c>
       <c r="L55">
         <f>-SUMIFS(H$3:H$25,J$3:J$25,K$53)+M55*5</f>
-        <v>-76</v>
+        <v>-140</v>
       </c>
       <c r="M55">
         <f>SUMIFS(Q$3:Q$25,J$3:J$25,K$53)-COUNTIFS(J$3:J$25,K$53,M$3:M$25,"*gộp*")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K56" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K57" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K58" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="11:13" ht="15" x14ac:dyDescent="0.25">
       <c r="L59" s="42">
         <f>SUBTOTAL(9,L54:L58)</f>
-        <v>9550</v>
+        <v>9545</v>
       </c>
       <c r="M59" s="42">
         <f>M54</f>
@@ -16245,5 +16271,6 @@
     <mergeCell ref="C33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03772D06-976D-45AE-B444-D87ABFB43E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E6C78B-B386-447D-BEDC-C00391C75760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <sheet name="27-03" sheetId="29" r:id="rId10"/>
     <sheet name="28-03" sheetId="30" r:id="rId11"/>
     <sheet name="30-03" sheetId="31" r:id="rId12"/>
-    <sheet name="31-03" sheetId="18" r:id="rId13"/>
+    <sheet name="31-03" sheetId="19" r:id="rId13"/>
     <sheet name="Sheet1" sheetId="32" r:id="rId14"/>
   </sheets>
   <definedNames>
@@ -40,7 +40,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'27-03'!$A$2:$P$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'28-03'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'30-03'!$A$2:$P$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'31-03'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'31-03'!$A$2:$P$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Sheet1!$A$2:$E$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="1255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="1257">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -3827,6 +3827,12 @@
   </si>
   <si>
     <t>at 31-03</t>
+  </si>
+  <si>
+    <t>1 đơn</t>
+  </si>
+  <si>
+    <t>3 đơn</t>
   </si>
 </sst>
 </file>
@@ -3978,7 +3984,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -4011,16 +4017,25 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4384,7 +4399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F928E1C-726F-4263-AEA3-2BEB923DF92E}">
   <dimension ref="A2:Q59"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
@@ -5383,10 +5398,10 @@
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="8" t="s">
         <v>89</v>
       </c>
@@ -5410,11 +5425,11 @@
       <c r="B30" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="38">
         <f>SUMIFS(G$3:G$24,B$3:B$24,A$29,L$3:L$24,A$30)</f>
         <v>12930</v>
       </c>
-      <c r="D30" s="39"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="7">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$29,L$3:L$24,A$30)</f>
         <v>22</v>
@@ -5445,11 +5460,11 @@
       <c r="B31" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="40">
+      <c r="C31" s="39">
         <f>-SUMIFS(H$3:H$111,$B$3:$B$111,$A29,$L$3:$L$111,$A30)</f>
         <v>-635</v>
       </c>
-      <c r="D31" s="40"/>
+      <c r="D31" s="39"/>
       <c r="E31">
         <f>SUMIFS(Q$3:Q$111,$B$3:$B$111,$A29,$L$3:$L$111,$A30)</f>
         <v>22</v>
@@ -5477,11 +5492,11 @@
       <c r="B32" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="39">
         <f>-SUMIFS(I$3:I$24,B$3:B$24,A$29,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
-      <c r="D32" s="40"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="6">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$29,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
@@ -5504,11 +5519,11 @@
       <c r="B33" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="37">
         <f>SUBTOTAL(9,C30:C32)</f>
         <v>12295</v>
       </c>
-      <c r="D33" s="38"/>
+      <c r="D33" s="37"/>
       <c r="E33">
         <f>E30</f>
         <v>22</v>
@@ -5528,8 +5543,8 @@
       <c r="B34" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
       <c r="K34" s="6" t="s">
         <v>103</v>
       </c>
@@ -5545,8 +5560,8 @@
       <c r="B35" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
       <c r="L35" s="12">
         <f>SUBTOTAL(9,L30:L34)</f>
         <v>3466</v>
@@ -5567,11 +5582,11 @@
       <c r="B37" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="36">
         <f>C33+C34+C35</f>
         <v>12295</v>
       </c>
-      <c r="D37" s="37"/>
+      <c r="D37" s="36"/>
       <c r="E37" s="5" t="s">
         <v>108</v>
       </c>
@@ -5783,7 +5798,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D2D7F8-C3E6-456E-A5D8-5637D43CE2EF}">
   <dimension ref="A2:Q71"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -7282,10 +7297,10 @@
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="4" t="s">
         <v>89</v>
       </c>
@@ -7313,11 +7328,11 @@
       <c r="B42" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="43">
         <f>SUMIFS(I$3:I$37,B$3:B$37,A$41,L$3:L$37,A$42)</f>
         <v>24400</v>
       </c>
-      <c r="D42" s="35"/>
+      <c r="D42" s="43"/>
       <c r="E42" s="3">
         <f>SUMIFS(Q$3:Q$37,B$3:B$37,A$41,L$3:L$37,A$42)</f>
         <v>35</v>
@@ -7352,10 +7367,10 @@
       <c r="B43" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="44">
         <v>0</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="44"/>
       <c r="K43" t="s">
         <v>96</v>
       </c>
@@ -7379,11 +7394,11 @@
       <c r="B44" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="44">
         <f>-SUMIFS(I$3:I$37,B$3:B$37,A$41,P$3:P$37,"xx",N$3:N$37,"x")</f>
         <v>0</v>
       </c>
-      <c r="D44" s="36"/>
+      <c r="D44" s="44"/>
       <c r="E44" s="2">
         <f>SUMIFS(Q$3:Q$37,B$3:B$37,A$41,P$3:P$37,"xx",N$3:N$37,"x")</f>
         <v>0</v>
@@ -7403,11 +7418,11 @@
       <c r="B45" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="42">
         <f>SUBTOTAL(9,C42:C44)</f>
         <v>24400</v>
       </c>
-      <c r="D45" s="34"/>
+      <c r="D45" s="42"/>
       <c r="E45">
         <f>E42</f>
         <v>35</v>
@@ -7427,8 +7442,8 @@
       <c r="B46" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
       <c r="K46" s="2" t="s">
         <v>103</v>
       </c>
@@ -7444,8 +7459,8 @@
       <c r="B47" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
       <c r="L47" s="31">
         <f>SUBTOTAL(9,L42:L46)</f>
         <v>6945</v>
@@ -7466,11 +7481,11 @@
       <c r="B49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="41">
         <f>C45+C46+C47</f>
         <v>24400</v>
       </c>
-      <c r="D49" s="33"/>
+      <c r="D49" s="41"/>
       <c r="E49" s="1" t="s">
         <v>108</v>
       </c>
@@ -7691,7 +7706,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{910DA1F4-1833-4FA2-92F1-E40412E68CE5}">
   <dimension ref="A2:Q55"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -8879,10 +8894,10 @@
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="4" t="s">
         <v>89</v>
       </c>
@@ -8910,11 +8925,11 @@
       <c r="B34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="43">
         <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>17750</v>
       </c>
-      <c r="D34" s="35"/>
+      <c r="D34" s="43"/>
       <c r="E34" s="3">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>27</v>
@@ -8949,10 +8964,10 @@
       <c r="B35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="44">
         <v>0</v>
       </c>
-      <c r="D35" s="36"/>
+      <c r="D35" s="44"/>
       <c r="K35" t="s">
         <v>96</v>
       </c>
@@ -8976,11 +8991,11 @@
       <c r="B36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="44">
         <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>0</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="44"/>
       <c r="E36" s="2">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>0</v>
@@ -9000,11 +9015,11 @@
       <c r="B37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="42">
         <f>SUBTOTAL(9,C34:C36)</f>
         <v>17750</v>
       </c>
-      <c r="D37" s="34"/>
+      <c r="D37" s="42"/>
       <c r="E37">
         <f>E34</f>
         <v>27</v>
@@ -9024,8 +9039,8 @@
       <c r="B38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
       <c r="K38" s="2" t="s">
         <v>103</v>
       </c>
@@ -9041,8 +9056,8 @@
       <c r="B39" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
       <c r="L39" s="31">
         <f>SUBTOTAL(9,L34:L38)</f>
         <v>7294</v>
@@ -9056,11 +9071,11 @@
       <c r="B41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="41">
         <f>C37+C38+C39</f>
         <v>17750</v>
       </c>
-      <c r="D41" s="33"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="1" t="s">
         <v>108</v>
       </c>
@@ -9218,7 +9233,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3743A2AE-DA74-48C7-B819-A85E917CF02D}">
   <dimension ref="A2:Q102"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -11939,10 +11954,10 @@
       <c r="A72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D72" s="34"/>
+      <c r="D72" s="42"/>
       <c r="E72" s="4" t="s">
         <v>89</v>
       </c>
@@ -11970,11 +11985,11 @@
       <c r="B73" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C73" s="35">
+      <c r="C73" s="43">
         <f>SUMIFS(I$3:I$68,B$3:B$68,A$72,L$3:L$68,A$73)</f>
         <v>34725</v>
       </c>
-      <c r="D73" s="35"/>
+      <c r="D73" s="43"/>
       <c r="E73" s="3">
         <f>SUMIFS(Q$3:Q$68,B$3:B$68,A$72,L$3:L$68,A$73)</f>
         <v>66</v>
@@ -12009,10 +12024,10 @@
       <c r="B74" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C74" s="36">
+      <c r="C74" s="44">
         <v>0</v>
       </c>
-      <c r="D74" s="36"/>
+      <c r="D74" s="44"/>
       <c r="K74" t="s">
         <v>96</v>
       </c>
@@ -12036,11 +12051,11 @@
       <c r="B75" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C75" s="36">
+      <c r="C75" s="44">
         <f>-SUMIFS(I$3:I$68,B$3:B$68,A$72,P$3:P$68,"xx",N$3:N$68,"x")</f>
         <v>0</v>
       </c>
-      <c r="D75" s="36"/>
+      <c r="D75" s="44"/>
       <c r="E75" s="2">
         <f>SUMIFS(Q$3:Q$68,B$3:B$68,A$72,P$3:P$68,"xx",N$3:N$68,"x")</f>
         <v>0</v>
@@ -12068,11 +12083,11 @@
       <c r="B76" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C76" s="34">
+      <c r="C76" s="42">
         <f>SUBTOTAL(9,C73:C75)</f>
         <v>34725</v>
       </c>
-      <c r="D76" s="34"/>
+      <c r="D76" s="42"/>
       <c r="E76">
         <f>E73</f>
         <v>66</v>
@@ -12092,8 +12107,8 @@
       <c r="B77" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
       <c r="K77" s="2" t="s">
         <v>103</v>
       </c>
@@ -12109,8 +12124,8 @@
       <c r="B78" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
       <c r="L78" s="31">
         <f>SUBTOTAL(9,L73:L77)</f>
         <v>8068</v>
@@ -12131,11 +12146,11 @@
       <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C80" s="33">
+      <c r="C80" s="41">
         <f>C76+C77+C78</f>
         <v>34725</v>
       </c>
-      <c r="D80" s="33"/>
+      <c r="D80" s="41"/>
       <c r="E80" s="1" t="s">
         <v>108</v>
       </c>
@@ -12342,7 +12357,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A2:Q60"/>
+  <dimension ref="A2:Q61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -12356,7 +12371,7 @@
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" customWidth="1"/>
     <col min="15" max="15" width="11.140625" customWidth="1"/>
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
@@ -13378,11 +13393,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="9">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I27" s="9">
         <f>-H27</f>
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -13498,7 +13513,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="18">
-        <f>G30-H30</f>
+        <f t="shared" ref="I30:I35" si="1">G30-H30</f>
         <v>580</v>
       </c>
       <c r="J30" s="17" t="s">
@@ -13543,14 +13558,14 @@
         <v>2</v>
       </c>
       <c r="G31" s="9">
-        <v>2945</v>
+        <v>2910</v>
       </c>
       <c r="H31" s="9">
         <v>35</v>
       </c>
       <c r="I31" s="9">
-        <f>G31-H31</f>
-        <v>2910</v>
+        <f t="shared" si="1"/>
+        <v>2875</v>
       </c>
       <c r="J31" t="s">
         <v>22</v>
@@ -13561,6 +13576,9 @@
       <c r="L31" t="s">
         <v>1189</v>
       </c>
+      <c r="M31" s="25" t="s">
+        <v>517</v>
+      </c>
       <c r="Q31" s="9">
         <v>1</v>
       </c>
@@ -13588,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="18">
-        <f>G32-H32</f>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J32" s="17" t="s">
@@ -13639,7 +13657,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="18">
-        <f>G33-H33</f>
+        <f t="shared" si="1"/>
         <v>590</v>
       </c>
       <c r="J33" s="17" t="s">
@@ -13690,7 +13708,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="18">
-        <f>G34-H34</f>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="J34" s="17" t="s">
@@ -13718,404 +13736,463 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D36" s="5">
-        <f>COUNTA(D3:D34)</f>
-        <v>28</v>
-      </c>
-      <c r="G36" s="5">
-        <f t="shared" ref="G36:Q36" si="1">SUBTOTAL(9,G3:G34)</f>
-        <v>17670</v>
-      </c>
-      <c r="H36" s="5">
+    <row r="35" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F35" s="18">
+        <v>4</v>
+      </c>
+      <c r="G35" s="18">
+        <v>745</v>
+      </c>
+      <c r="H35" s="18">
+        <v>0</v>
+      </c>
+      <c r="I35" s="18">
         <f t="shared" si="1"/>
-        <v>805</v>
-      </c>
-      <c r="I36" s="5">
-        <f t="shared" si="1"/>
-        <v>16865</v>
-      </c>
-      <c r="J36" s="5">
-        <f t="shared" si="1"/>
+        <v>745</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>1003</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="O35" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="P35" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q35" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D37" s="5">
+        <f>COUNTA(D3:D35)</f>
+        <v>29</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" ref="G37:Q37" si="2">SUBTOTAL(9,G3:G35)</f>
+        <v>18380</v>
+      </c>
+      <c r="H37" s="5">
+        <f t="shared" si="2"/>
+        <v>815</v>
+      </c>
+      <c r="I37" s="5">
+        <f t="shared" si="2"/>
+        <v>17565</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="5">
-        <f t="shared" si="1"/>
+      <c r="K37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="5">
-        <f t="shared" si="1"/>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M36" s="5">
-        <f t="shared" si="1"/>
+      <c r="M37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N36" s="5">
-        <f t="shared" si="1"/>
+      <c r="N37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O36" s="5">
-        <f t="shared" si="1"/>
+      <c r="O37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P36" s="5">
-        <f t="shared" si="1"/>
+      <c r="P37" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="5">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H37">
+      <c r="Q37" s="5">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H38">
         <f>-6*17</f>
         <v>-102</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="38" t="s">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="8" t="s">
+      <c r="D39" s="37"/>
+      <c r="E39" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H38">
+      <c r="H39">
         <f>-4*25</f>
         <v>-100</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K39" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M39" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="O39" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>1189</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="39">
-        <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
-        <v>14235</v>
-      </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="7">
-        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+      <c r="C40" s="38">
+        <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
+        <v>14190</v>
+      </c>
+      <c r="D40" s="38"/>
+      <c r="E40" s="7">
+        <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>28</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>93</v>
       </c>
-      <c r="H39">
+      <c r="H40">
         <f>-2*30</f>
         <v>-60</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K40" t="s">
         <v>94</v>
       </c>
-      <c r="L39">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$38)</f>
+      <c r="L40">
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$39)</f>
         <v>4225</v>
       </c>
-      <c r="M39">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)</f>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$39)</f>
         <v>7</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O40" t="s">
         <v>79</v>
       </c>
-      <c r="P39">
-        <f>L44</f>
-        <v>3510</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="40">
-        <v>0</v>
-      </c>
-      <c r="D40" s="40"/>
-      <c r="K40" t="s">
-        <v>96</v>
-      </c>
-      <c r="L40">
-        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$38)+M40*5</f>
-        <v>-135</v>
-      </c>
-      <c r="M40">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")</f>
-        <v>7</v>
-      </c>
-      <c r="O40" t="s">
-        <v>1254</v>
-      </c>
       <c r="P40">
-        <f>L52</f>
-        <v>3063</v>
+        <f>L45</f>
+        <v>2760</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="39">
+        <v>0</v>
+      </c>
+      <c r="D41" s="39"/>
+      <c r="K41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L41">
+        <f>-SUMIFS(H$3:H$35,J$3:J$35,K$39)+M41*5</f>
+        <v>-135</v>
+      </c>
+      <c r="M41">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$39)-COUNTIFS(J$3:J$35,K$39,M$3:M$35,"*gộp*")</f>
+        <v>7</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1254</v>
+      </c>
+      <c r="P41">
+        <f>L53</f>
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="40">
-        <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
-        <v>-2630</v>
-      </c>
-      <c r="D41" s="40"/>
-      <c r="E41" s="6">
-        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
-        <v>4</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="C42" s="39">
+        <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
+        <v>-3375</v>
+      </c>
+      <c r="D42" s="39"/>
+      <c r="E42" s="6">
+        <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
+        <v>5</v>
+      </c>
+      <c r="K42" t="s">
         <v>98</v>
       </c>
-      <c r="O41" t="s">
-        <v>22</v>
-      </c>
-      <c r="P41">
-        <f>L60</f>
-        <v>5167</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
+      <c r="O42" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42">
+        <f>L61</f>
+        <v>5122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="38">
-        <f>SUBTOTAL(9,C39:C41)</f>
-        <v>11605</v>
-      </c>
-      <c r="D42" s="38"/>
-      <c r="E42">
-        <f>E39</f>
+      <c r="C43" s="37">
+        <f>SUBTOTAL(9,C40:C42)</f>
+        <v>10815</v>
+      </c>
+      <c r="D43" s="37"/>
+      <c r="E43">
+        <f>E40</f>
         <v>28</v>
       </c>
-      <c r="K42" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="L42" s="9">
-        <f>-I30</f>
-        <v>-580</v>
-      </c>
-      <c r="O42" t="s">
+      <c r="L43" s="6">
+        <v>-585</v>
+      </c>
+      <c r="M43" s="32" t="s">
+        <v>1255</v>
+      </c>
+      <c r="O43" t="s">
         <v>104</v>
       </c>
-      <c r="P42">
-        <f>-C46</f>
-        <v>-11605</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+      <c r="P43">
+        <f>-C47</f>
+        <v>-10815</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="K43" s="6" t="s">
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="K44" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O43" s="8" t="s">
+      <c r="L44" s="17">
+        <v>-745</v>
+      </c>
+      <c r="M44" s="32"/>
+      <c r="O44" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="P43" s="8">
-        <f>SUBTOTAL(9,P39:P42)</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="13" t="s">
+      <c r="P44" s="8">
+        <f>SUBTOTAL(9,P40:P43)</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B45" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="L44" s="12">
-        <f>SUBTOTAL(9,L39:L43)</f>
-        <v>3510</v>
-      </c>
-      <c r="M44" s="12">
-        <f>M39</f>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="L45" s="12">
+        <f>SUBTOTAL(9,L40:L44)</f>
+        <v>2760</v>
+      </c>
+      <c r="M45" s="33">
+        <f>M40</f>
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B46" s="5" t="s">
+      <c r="M46" s="32"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C46" s="37">
-        <f>C42+C43+C44</f>
-        <v>11605</v>
-      </c>
-      <c r="D46" s="37"/>
-      <c r="E46" s="5" t="s">
+      <c r="C47" s="36">
+        <f>C43+C44+C45</f>
+        <v>10815</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K47" s="11" t="s">
         <v>1193</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L47" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M47" s="34" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K47" t="s">
-        <v>94</v>
-      </c>
-      <c r="L47">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$46)</f>
-        <v>5375</v>
-      </c>
-      <c r="M47">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)</f>
-        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L48">
-        <f>SUM(H37:H39)</f>
-        <v>-262</v>
-      </c>
-      <c r="M48">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)</f>
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$47)</f>
+        <v>5375</v>
+      </c>
+      <c r="M48" s="32">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$47)</f>
         <v>12</v>
       </c>
     </row>
     <row r="49" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
+        <v>96</v>
+      </c>
+      <c r="L49">
+        <f>SUM(H38:H40)</f>
+        <v>-262</v>
+      </c>
+      <c r="M49" s="32">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$47)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K50" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="L50" s="9">
-        <f>-SUM(I32:I34)</f>
-        <v>-2050</v>
-      </c>
+      <c r="M50" s="32"/>
     </row>
     <row r="51" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="L51" s="18">
+        <v>-2114</v>
+      </c>
+      <c r="M51" s="32" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L52" s="12">
-        <f>SUBTOTAL(9,L47:L51)</f>
-        <v>3063</v>
-      </c>
-      <c r="M52" s="12">
-        <f>M47</f>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L53" s="12">
+        <f>SUBTOTAL(9,L48:L52)</f>
+        <v>2999</v>
+      </c>
+      <c r="M53" s="12">
+        <f>M48</f>
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L54" s="11" t="s">
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M55" s="11" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K55" t="s">
-        <v>94</v>
-      </c>
-      <c r="L55">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$54)</f>
-        <v>5440</v>
-      </c>
-      <c r="M55">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)</f>
-        <v>9</v>
       </c>
     </row>
     <row r="56" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K56" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L56">
-        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$54)+M56*5</f>
-        <v>-225</v>
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$55)</f>
+        <v>5405</v>
       </c>
       <c r="M56">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")</f>
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$55)</f>
         <v>9</v>
       </c>
     </row>
     <row r="57" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K57" t="s">
+        <v>96</v>
+      </c>
+      <c r="L57">
+        <f>-SUMIFS(H$3:H$35,J$3:J$35,K$55)+M57*5</f>
+        <v>-235</v>
+      </c>
+      <c r="M57">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$55)-COUNTIFS(J$3:J$35,K$55,M$3:M$35,"*gộp*")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
         <v>98</v>
       </c>
-      <c r="L57">
-        <f>-M57*2</f>
+      <c r="L58">
+        <f>-M58*2</f>
         <v>-48</v>
       </c>
-      <c r="M57">
-        <f>E39-E41-(COUNTIFS(M$3:M$34,"*gộp*")/2)</f>
+      <c r="M58">
+        <f>E40-(COUNTIFS(M$3:M$35,"*đơn trả*")-(COUNTIFS(M$3:M$35,"*gộp*")/2))</f>
         <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K58" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="59" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K59" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K60" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L60" s="12">
-        <f>SUBTOTAL(9,L55:L59)</f>
-        <v>5167</v>
-      </c>
-      <c r="M60" s="12">
-        <f>M55</f>
+    <row r="61" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L61" s="12">
+        <f>SUBTOTAL(9,L56:L60)</f>
+        <v>5122</v>
+      </c>
+      <c r="M61" s="12">
+        <f>M56</f>
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
+  <autoFilter ref="A2:P35" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
   <mergeCells count="8">
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14334,12 +14411,16 @@
       <c r="A15" s="22">
         <v>46112</v>
       </c>
-      <c r="B15" s="23"/>
+      <c r="B15" s="23">
+        <v>28</v>
+      </c>
       <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23">
+        <v>4</v>
+      </c>
       <c r="E15" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -14348,7 +14429,7 @@
       </c>
       <c r="E16" s="24">
         <f>SUBTOTAL(9,E3:E15)</f>
-        <v>390</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
@@ -14356,8 +14437,8 @@
         <v>1183</v>
       </c>
       <c r="E17" s="24">
-        <f>SUM('17-03'!P35,'18-03'!P32,'19-03'!P47,'20-03'!P37,'21-03'!P44,'23-03'!P87,'24-03'!P27,'25-03'!P28,'26-03'!P43,'27-03'!P47,'28-03'!P38,'30-03'!P78)</f>
-        <v>1806</v>
+        <f>SUM('17-03'!P35,'18-03'!P32,'19-03'!P47,'20-03'!P37,'21-03'!P44,'23-03'!P87,'24-03'!P27,'25-03'!P28,'26-03'!P43,'27-03'!P47,'28-03'!P38,'30-03'!P78,'31-03'!P44)</f>
+        <v>1872</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
@@ -14366,7 +14447,7 @@
       </c>
       <c r="E18" s="24">
         <f>-E16*2</f>
-        <v>-780</v>
+        <v>-828</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
@@ -14375,7 +14456,7 @@
       </c>
       <c r="E19" s="24">
         <f>SUBTOTAL(9,E17:E18)</f>
-        <v>1026</v>
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
@@ -14388,7 +14469,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EBDAD0-3888-417E-AED0-7E9D32960B8F}">
   <dimension ref="A1:Q49"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
@@ -15338,10 +15419,10 @@
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="38"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="8" t="s">
         <v>89</v>
       </c>
@@ -15365,11 +15446,11 @@
       <c r="B28" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="40">
         <f>SUMIFS(I$3:I$22,B$3:B$22,A$27,L$3:L$22,A$28)</f>
         <v>11520</v>
       </c>
-      <c r="D28" s="39"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="7">
         <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,L$3:L$22,A$28)</f>
         <v>19</v>
@@ -15400,10 +15481,10 @@
       <c r="B29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="40">
+      <c r="C29" s="39">
         <v>0</v>
       </c>
-      <c r="D29" s="40"/>
+      <c r="D29" s="39"/>
       <c r="K29" t="s">
         <v>96</v>
       </c>
@@ -15427,11 +15508,11 @@
       <c r="B30" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="39">
         <f>-SUMIFS(I$3:I$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
         <v>-750</v>
       </c>
-      <c r="D30" s="40"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="6">
         <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
         <v>1</v>
@@ -15451,11 +15532,11 @@
       <c r="B31" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="37">
         <f>SUBTOTAL(9,C28:C30)</f>
         <v>10770</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="37"/>
       <c r="E31">
         <f>E28</f>
         <v>19</v>
@@ -15475,8 +15556,8 @@
       <c r="B32" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
       <c r="K32" s="6" t="s">
         <v>103</v>
       </c>
@@ -15495,8 +15576,8 @@
       <c r="B33" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
       <c r="L33" s="12">
         <f>SUBTOTAL(9,L28:L32)</f>
         <v>4134</v>
@@ -15510,11 +15591,11 @@
       <c r="B35" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="36">
         <f>C31+C32+C33</f>
         <v>10770</v>
       </c>
-      <c r="D35" s="37"/>
+      <c r="D35" s="36"/>
       <c r="E35" s="5" t="s">
         <v>108</v>
       </c>
@@ -17063,10 +17144,10 @@
       <c r="A41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="38"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="8" t="s">
         <v>89</v>
       </c>
@@ -17090,11 +17171,11 @@
       <c r="B42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="38">
         <f>SUMIFS(I$3:I$34,B$3:B$34,A$41,L$3:L$34,A$42)</f>
         <v>23940</v>
       </c>
-      <c r="D42" s="39"/>
+      <c r="D42" s="38"/>
       <c r="E42" s="7">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$41,L$3:L$34,A$42)</f>
         <v>32</v>
@@ -17125,10 +17206,10 @@
       <c r="B43" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="40">
+      <c r="C43" s="39">
         <v>0</v>
       </c>
-      <c r="D43" s="40"/>
+      <c r="D43" s="39"/>
       <c r="K43" t="s">
         <v>96</v>
       </c>
@@ -17152,11 +17233,11 @@
       <c r="B44" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="40">
+      <c r="C44" s="39">
         <f>-SUMIFS(I$3:I$34,B$3:B$34,A$41,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
       </c>
-      <c r="D44" s="40"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="6">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$41,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
@@ -17180,11 +17261,11 @@
       <c r="B45" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="37">
         <f>SUBTOTAL(9,C42:C44)</f>
         <v>23940</v>
       </c>
-      <c r="D45" s="38"/>
+      <c r="D45" s="37"/>
       <c r="E45">
         <f>E42</f>
         <v>32</v>
@@ -17204,8 +17285,8 @@
       <c r="B46" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
       <c r="K46" s="6" t="s">
         <v>103</v>
       </c>
@@ -17221,8 +17302,8 @@
       <c r="B47" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
       <c r="L47" s="14">
         <f>SUBTOTAL(9,L42:L46)</f>
         <v>4496</v>
@@ -17243,11 +17324,11 @@
       <c r="B49" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="36">
         <f>C45+C46+C47</f>
         <v>23940</v>
       </c>
-      <c r="D49" s="37"/>
+      <c r="D49" s="36"/>
       <c r="E49" s="5" t="s">
         <v>108</v>
       </c>
@@ -18581,10 +18662,10 @@
       <c r="A31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="37"/>
       <c r="E31" s="8" t="s">
         <v>89</v>
       </c>
@@ -18612,11 +18693,11 @@
       <c r="B32" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="39">
+      <c r="C32" s="38">
         <f>SUMIFS(I$3:I$27,B$3:B$27,A$31,L$3:L$27,A$32)</f>
         <v>8730</v>
       </c>
-      <c r="D32" s="39"/>
+      <c r="D32" s="38"/>
       <c r="E32" s="7">
         <f>SUMIFS(Q$3:Q$27,B$3:B$27,A$31,L$3:L$27,A$32)</f>
         <v>24</v>
@@ -18651,10 +18732,10 @@
       <c r="B33" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C33" s="39">
         <v>0</v>
       </c>
-      <c r="D33" s="40"/>
+      <c r="D33" s="39"/>
       <c r="K33" t="s">
         <v>96</v>
       </c>
@@ -18678,11 +18759,11 @@
       <c r="B34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="39">
         <f>-SUMIFS(I$3:I$27,B$3:B$27,A$31,P$3:P$27,"xx",N$3:N$27,"x")</f>
         <v>-1450</v>
       </c>
-      <c r="D34" s="40"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="6">
         <f>SUMIFS(Q$3:Q$27,B$3:B$27,A$31,P$3:P$27,"xx",N$3:N$27,"x")</f>
         <v>1</v>
@@ -18702,11 +18783,11 @@
       <c r="B35" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="37">
         <f>SUBTOTAL(9,C32:C34)</f>
         <v>7280</v>
       </c>
-      <c r="D35" s="38"/>
+      <c r="D35" s="37"/>
       <c r="E35">
         <f>E32</f>
         <v>24</v>
@@ -18726,8 +18807,8 @@
       <c r="B36" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
       <c r="K36" s="6" t="s">
         <v>103</v>
       </c>
@@ -18743,8 +18824,8 @@
       <c r="B37" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
       <c r="L37" s="12">
         <f>SUBTOTAL(9,L32:L36)</f>
         <v>2454</v>
@@ -18765,11 +18846,11 @@
       <c r="B39" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="36">
         <f>C35+C36+C37</f>
         <v>7280</v>
       </c>
-      <c r="D39" s="37"/>
+      <c r="D39" s="36"/>
       <c r="E39" s="5" t="s">
         <v>108</v>
       </c>
@@ -18993,7 +19074,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCEB95DE-B6A2-48BA-8E2F-4C2148BC1688}">
   <dimension ref="A2:Q61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -20427,10 +20508,10 @@
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="34"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="4" t="s">
         <v>89</v>
       </c>
@@ -20458,11 +20539,11 @@
       <c r="B40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="43">
         <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>15930</v>
       </c>
-      <c r="D40" s="35"/>
+      <c r="D40" s="43"/>
       <c r="E40" s="3">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>32</v>
@@ -20497,10 +20578,10 @@
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="44">
         <v>0</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="44"/>
       <c r="K41" t="s">
         <v>96</v>
       </c>
@@ -20524,11 +20605,11 @@
       <c r="B42" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="44">
         <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>-820</v>
       </c>
-      <c r="D42" s="36"/>
+      <c r="D42" s="44"/>
       <c r="E42" s="2">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>1</v>
@@ -20548,11 +20629,11 @@
       <c r="B43" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="42">
         <f>SUBTOTAL(9,C40:C42)</f>
         <v>15110</v>
       </c>
-      <c r="D43" s="34"/>
+      <c r="D43" s="42"/>
       <c r="E43">
         <f>E40</f>
         <v>32</v>
@@ -20572,8 +20653,8 @@
       <c r="B44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
       <c r="K44" s="2" t="s">
         <v>103</v>
       </c>
@@ -20589,8 +20670,8 @@
       <c r="B45" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
       <c r="L45" s="31">
         <f>SUBTOTAL(9,L40:L44)</f>
         <v>1635</v>
@@ -20604,11 +20685,11 @@
       <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="41">
         <f>C43+C44+C45</f>
         <v>15110</v>
       </c>
-      <c r="D47" s="33"/>
+      <c r="D47" s="41"/>
       <c r="E47" s="1" t="s">
         <v>108</v>
       </c>
@@ -20769,7 +20850,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1464CBDD-EEFF-47C4-BEAE-9713391EFAA9}">
   <dimension ref="A2:Q111"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -23868,10 +23949,10 @@
       <c r="A81" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C81" s="34" t="s">
+      <c r="C81" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D81" s="34"/>
+      <c r="D81" s="42"/>
       <c r="E81" s="4" t="s">
         <v>89</v>
       </c>
@@ -23899,11 +23980,11 @@
       <c r="B82" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C82" s="35">
+      <c r="C82" s="43">
         <f>SUMIFS(I$3:I$77,B$3:B$77,A$81,L$3:L$77,A$82)</f>
         <v>53935</v>
       </c>
-      <c r="D82" s="35"/>
+      <c r="D82" s="43"/>
       <c r="E82" s="3">
         <f>SUMIFS(Q$3:Q$77,B$3:B$77,A$81,L$3:L$77,A$82)</f>
         <v>73</v>
@@ -23938,10 +24019,10 @@
       <c r="B83" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C83" s="36">
+      <c r="C83" s="44">
         <v>0</v>
       </c>
-      <c r="D83" s="36"/>
+      <c r="D83" s="44"/>
       <c r="K83" t="s">
         <v>96</v>
       </c>
@@ -23965,11 +24046,11 @@
       <c r="B84" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C84" s="36">
+      <c r="C84" s="44">
         <f>-SUMIFS(I$3:I$77,B$3:B$77,A$81,P$3:P$77,"xx",N$3:N$77,"x")</f>
         <v>-2430</v>
       </c>
-      <c r="D84" s="36"/>
+      <c r="D84" s="44"/>
       <c r="E84" s="2">
         <f>SUMIFS(Q$3:Q$77,B$3:B$77,A$81,P$3:P$77,"xx",N$3:N$77,"x")</f>
         <v>3</v>
@@ -23989,11 +24070,11 @@
       <c r="B85" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C85" s="34">
+      <c r="C85" s="42">
         <f>SUBTOTAL(9,C82:C84)</f>
         <v>51505</v>
       </c>
-      <c r="D85" s="34"/>
+      <c r="D85" s="42"/>
       <c r="E85">
         <f>E82</f>
         <v>73</v>
@@ -24013,8 +24094,8 @@
       <c r="B86" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
       <c r="K86" s="2" t="s">
         <v>103</v>
       </c>
@@ -24030,8 +24111,8 @@
       <c r="B87" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
       <c r="L87" s="31">
         <f>SUBTOTAL(9,L82:L86)</f>
         <v>16790</v>
@@ -24052,11 +24133,11 @@
       <c r="B89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C89" s="33">
+      <c r="C89" s="41">
         <f>C85+C86+C87</f>
         <v>51505</v>
       </c>
-      <c r="D89" s="33"/>
+      <c r="D89" s="41"/>
       <c r="E89" s="1" t="s">
         <v>108</v>
       </c>
@@ -24279,7 +24360,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB2F39C-5A0B-4E3B-A4D8-ABFD710251D1}">
   <dimension ref="A2:Q37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -25077,10 +25158,10 @@
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="4" t="s">
         <v>89</v>
       </c>
@@ -25108,11 +25189,11 @@
       <c r="B24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="43">
         <f>SUMIFS(I$3:I$19,B$3:B$19,A$23,L$3:L$19,A$24)</f>
         <v>7290</v>
       </c>
-      <c r="D24" s="35"/>
+      <c r="D24" s="43"/>
       <c r="E24" s="3">
         <f>SUMIFS(Q$3:Q$19,B$3:B$19,A$23,L$3:L$19,A$24)</f>
         <v>17</v>
@@ -25147,10 +25228,10 @@
       <c r="B25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="44">
         <v>0</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="44"/>
       <c r="K25" t="s">
         <v>96</v>
       </c>
@@ -25174,11 +25255,11 @@
       <c r="B26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="44">
         <f>-SUMIFS(I$3:I$19,B$3:B$19,A$23,P$3:P$19,"xx",N$3:N$19,"x")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="44"/>
       <c r="E26" s="2">
         <f>SUMIFS(Q$3:Q$19,B$3:B$19,A$23,P$3:P$19,"xx",N$3:N$19,"x")</f>
         <v>0</v>
@@ -25206,11 +25287,11 @@
       <c r="B27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="42">
         <f>SUBTOTAL(9,C24:C26)</f>
         <v>7290</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="42"/>
       <c r="E27">
         <f>E24</f>
         <v>17</v>
@@ -25230,8 +25311,8 @@
       <c r="B28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
       <c r="K28" s="2" t="s">
         <v>103</v>
       </c>
@@ -25240,8 +25321,8 @@
       <c r="B29" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
       <c r="L29" s="31">
         <f>SUBTOTAL(9,L24:L28)</f>
         <v>2291</v>
@@ -25255,11 +25336,11 @@
       <c r="B31" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="41">
         <f>C27+C28+C29</f>
         <v>7290</v>
       </c>
-      <c r="D31" s="33"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="1" t="s">
         <v>108</v>
       </c>
@@ -25347,7 +25428,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E36D51-6036-4A99-9D24-714E67332C6E}">
   <dimension ref="A2:Q45"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -26141,10 +26222,10 @@
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="4" t="s">
         <v>89</v>
       </c>
@@ -26172,11 +26253,11 @@
       <c r="B24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="43">
         <f>SUMIFS(I$3:I$19,B$3:B$19,A$23,L$3:L$19,A$24)</f>
         <v>9720</v>
       </c>
-      <c r="D24" s="35"/>
+      <c r="D24" s="43"/>
       <c r="E24" s="3">
         <f>SUMIFS(Q$3:Q$19,B$3:B$19,A$23,L$3:L$19,A$24)</f>
         <v>17</v>
@@ -26207,10 +26288,10 @@
       <c r="B25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="44">
         <v>0</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="44"/>
       <c r="K25" t="s">
         <v>96</v>
       </c>
@@ -26234,11 +26315,11 @@
       <c r="B26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="44">
         <f>-SUMIFS(I$3:I$19,B$3:B$19,A$23,P$3:P$19,"xx",N$3:N$19,"x")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="44"/>
       <c r="E26" s="2">
         <f>SUMIFS(Q$3:Q$19,B$3:B$19,A$23,P$3:P$19,"xx",N$3:N$19,"x")</f>
         <v>0</v>
@@ -26258,11 +26339,11 @@
       <c r="B27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="42">
         <f>SUBTOTAL(9,C24:C26)</f>
         <v>9720</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="42"/>
       <c r="E27">
         <f>E24</f>
         <v>17</v>
@@ -26282,8 +26363,8 @@
       <c r="B28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
       <c r="K28" s="2" t="s">
         <v>103</v>
       </c>
@@ -26299,8 +26380,8 @@
       <c r="B29" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
       <c r="L29" s="31">
         <f>SUBTOTAL(9,L24:L28)</f>
         <v>5319</v>
@@ -26314,11 +26395,11 @@
       <c r="B31" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="41">
         <f>C27+C28+C29</f>
         <v>9720</v>
       </c>
-      <c r="D31" s="33"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="1" t="s">
         <v>108</v>
       </c>
@@ -26476,7 +26557,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34A90C4-C6DD-4189-8E34-D7285CDD91D0}">
   <dimension ref="A2:Q67"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -27838,10 +27919,10 @@
       <c r="A37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="34"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="4" t="s">
         <v>89</v>
       </c>
@@ -27869,11 +27950,11 @@
       <c r="B38" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="43">
         <f>SUMIFS(I$3:I$33,B$3:B$33,A$37,L$3:L$33,A$38)</f>
         <v>17230</v>
       </c>
-      <c r="D38" s="35"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="3">
         <f>SUMIFS(Q$3:Q$33,B$3:B$33,A$37,L$3:L$33,A$38)</f>
         <v>31</v>
@@ -27908,10 +27989,10 @@
       <c r="B39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="44">
         <v>0</v>
       </c>
-      <c r="D39" s="36"/>
+      <c r="D39" s="44"/>
       <c r="K39" t="s">
         <v>96</v>
       </c>
@@ -27935,11 +28016,11 @@
       <c r="B40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="44">
         <f>-SUMIFS(I$3:I$33,B$3:B$33,A$37,P$3:P$33,"xx",N$3:N$33,"x")</f>
         <v>-870</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="44"/>
       <c r="E40" s="2">
         <f>SUMIFS(Q$3:Q$33,B$3:B$33,A$37,P$3:P$33,"xx",N$3:N$33,"x")</f>
         <v>1</v>
@@ -27967,11 +28048,11 @@
       <c r="B41" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="42">
         <f>SUBTOTAL(9,C38:C40)</f>
         <v>16360</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="42"/>
       <c r="E41">
         <f>E38</f>
         <v>31</v>
@@ -27991,8 +28072,8 @@
       <c r="B42" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
       <c r="K42" s="2" t="s">
         <v>103</v>
       </c>
@@ -28008,8 +28089,8 @@
       <c r="B43" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
       <c r="L43" s="31">
         <f>SUBTOTAL(9,L38:L42)</f>
         <v>3185</v>
@@ -28030,11 +28111,11 @@
       <c r="B45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="41">
         <f>C41+C42+C43</f>
         <v>16360</v>
       </c>
-      <c r="D45" s="33"/>
+      <c r="D45" s="41"/>
       <c r="E45" s="1" t="s">
         <v>108</v>
       </c>

--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E6C78B-B386-447D-BEDC-C00391C75760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E458806-5293-4F5E-9B46-94AC8182F15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
   </bookViews>
@@ -55,6 +55,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>

--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E458806-5293-4F5E-9B46-94AC8182F15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150506C8-6D1C-4929-886A-C8BA00107067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
   </bookViews>

--- a/data/Mar/Bảng-đối-soát-t3-2026.xlsx
+++ b/data/Mar/Bảng-đối-soát-t3-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150506C8-6D1C-4929-886A-C8BA00107067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04048687-BE3E-47BA-BDCC-8D47FD3CB952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{7DBF314D-BB0B-41C9-BACA-A4F738DC8062}"/>
   </bookViews>
